--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-statut.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-statut.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4022" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4022" uniqueCount="385">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -414,9 +414,6 @@
     <t>iheSimpleObservation</t>
   </si>
   <si>
-    <t xml:space="preserve"> Conformité Simple observation (IHE PCC)</t>
-  </si>
-  <si>
     <t>Conformité Simple observation (IHE PCC)</t>
   </si>
   <si>
@@ -917,7 +914,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>
@@ -2737,7 +2734,7 @@
         <v>129</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2808,10 +2805,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2909,10 +2906,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3012,10 +3009,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3115,10 +3112,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3147,7 +3144,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3159,7 +3156,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -3218,10 +3215,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3321,13 +3318,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>75</v>
@@ -3352,10 +3349,10 @@
         <v>96</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3426,10 +3423,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3527,10 +3524,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3630,10 +3627,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3733,10 +3730,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3765,7 +3762,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3777,7 +3774,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -3836,10 +3833,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3939,13 +3936,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3970,10 +3967,10 @@
         <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4044,10 +4041,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4145,10 +4142,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4248,10 +4245,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4351,10 +4348,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4383,7 +4380,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4395,7 +4392,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4454,10 +4451,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4557,10 +4554,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4574,7 +4571,7 @@
         <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>75</v>
@@ -4597,7 +4594,7 @@
         <v>75</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>75</v>
@@ -4616,7 +4613,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -4634,7 +4631,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4654,10 +4651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4671,7 +4668,7 @@
         <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>75</v>
@@ -4694,7 +4691,7 @@
         <v>75</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>75</v>
@@ -4713,7 +4710,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -4731,7 +4728,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4751,10 +4748,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4830,7 +4827,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -4850,10 +4847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4867,7 +4864,7 @@
         <v>76</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>75</v>
@@ -4879,10 +4876,10 @@
         <v>96</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4933,7 +4930,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4953,10 +4950,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4979,7 +4976,7 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -5032,7 +5029,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5052,10 +5049,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5069,7 +5066,7 @@
         <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
@@ -5078,11 +5075,11 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5109,11 +5106,11 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5131,7 +5128,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5151,10 +5148,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5252,10 +5249,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5271,7 +5268,7 @@
         <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>75</v>
@@ -5284,7 +5281,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5296,46 +5293,46 @@
         <v>75</v>
       </c>
       <c r="S37" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5355,17 +5352,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>76</v>
@@ -5374,7 +5371,7 @@
         <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>75</v>
@@ -5387,7 +5384,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5399,46 +5396,46 @@
         <v>75</v>
       </c>
       <c r="S38" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5458,17 +5455,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>81</v>
@@ -5490,7 +5487,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5502,46 +5499,46 @@
         <v>75</v>
       </c>
       <c r="S39" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5561,17 +5558,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>81</v>
@@ -5593,7 +5590,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5644,7 +5641,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5664,17 +5661,17 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>81</v>
@@ -5683,7 +5680,7 @@
         <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>75</v>
@@ -5696,7 +5693,7 @@
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5708,46 +5705,46 @@
         <v>75</v>
       </c>
       <c r="S41" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5767,10 +5764,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5793,11 +5790,11 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5848,7 +5845,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -5868,10 +5865,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5898,7 +5895,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5949,7 +5946,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -5969,39 +5966,39 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6052,7 +6049,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6072,17 +6069,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -6100,11 +6097,11 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6155,7 +6152,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6175,17 +6172,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>81</v>
@@ -6203,11 +6200,11 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6258,7 +6255,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6278,10 +6275,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6304,7 +6301,7 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6357,7 +6354,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6377,10 +6374,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6394,7 +6391,7 @@
         <v>76</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>75</v>
@@ -6403,10 +6400,10 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -6458,7 +6455,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6478,10 +6475,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6579,17 +6576,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>81</v>
@@ -6611,7 +6608,7 @@
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6642,25 +6639,25 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6680,39 +6677,39 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E51" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="F51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6763,7 +6760,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6783,17 +6780,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>81</v>
@@ -6815,7 +6812,7 @@
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6846,25 +6843,25 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6884,17 +6881,17 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>81</v>
@@ -6916,7 +6913,7 @@
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6967,7 +6964,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -6987,17 +6984,17 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>81</v>
@@ -7019,7 +7016,7 @@
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7046,29 +7043,29 @@
         <v>75</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -7088,10 +7085,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7147,25 +7144,25 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7185,10 +7182,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7214,13 +7211,13 @@
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7270,7 +7267,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7290,39 +7287,39 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E57" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="F57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7373,7 +7370,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7393,17 +7390,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>81</v>
@@ -7421,11 +7418,11 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7476,19 +7473,19 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -7496,10 +7493,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7513,7 +7510,7 @@
         <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>75</v>
@@ -7525,10 +7522,10 @@
         <v>92</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7559,7 +7556,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -7577,7 +7574,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7597,10 +7594,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7698,10 +7695,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7730,7 +7727,7 @@
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7742,7 +7739,7 @@
         <v>75</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>75</v>
@@ -7781,7 +7778,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7801,17 +7798,17 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>81</v>
@@ -7833,7 +7830,7 @@
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7884,7 +7881,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -7904,17 +7901,17 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>81</v>
@@ -7936,7 +7933,7 @@
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7987,7 +7984,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8007,17 +8004,17 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>81</v>
@@ -8039,7 +8036,7 @@
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8090,7 +8087,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8110,17 +8107,17 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>81</v>
@@ -8142,7 +8139,7 @@
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8193,7 +8190,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8213,10 +8210,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8239,11 +8236,11 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8294,7 +8291,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8314,10 +8311,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8344,7 +8341,7 @@
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8395,7 +8392,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8415,39 +8412,39 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E68" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K68" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="F68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8498,7 +8495,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8518,39 +8515,39 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E69" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K69" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="F69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8601,7 +8598,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8621,17 +8618,17 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>81</v>
@@ -8649,11 +8646,11 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8704,7 +8701,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -8724,10 +8721,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8741,7 +8738,7 @@
         <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>75</v>
@@ -8750,13 +8747,13 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L71" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="M71" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8807,7 +8804,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -8827,10 +8824,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8853,7 +8850,7 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8882,11 +8879,11 @@
         <v>75</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>75</v>
@@ -8904,7 +8901,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -8924,10 +8921,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8950,7 +8947,7 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -9003,7 +9000,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -9023,10 +9020,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9082,7 +9079,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -9100,7 +9097,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9120,10 +9117,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9137,7 +9134,7 @@
         <v>76</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>75</v>
@@ -9146,10 +9143,10 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -9201,7 +9198,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9221,10 +9218,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9322,10 +9319,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9354,7 +9351,7 @@
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9405,7 +9402,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -9425,17 +9422,17 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>81</v>
@@ -9457,7 +9454,7 @@
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9508,7 +9505,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -9528,17 +9525,17 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>81</v>
@@ -9560,7 +9557,7 @@
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9611,7 +9608,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9631,17 +9628,17 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>81</v>
@@ -9663,7 +9660,7 @@
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9714,7 +9711,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9734,17 +9731,17 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>81</v>
@@ -9766,7 +9763,7 @@
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9817,7 +9814,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -9837,10 +9834,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9863,11 +9860,11 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9918,7 +9915,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -9938,10 +9935,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9968,7 +9965,7 @@
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10019,7 +10016,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -10039,39 +10036,39 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E84" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K84" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="F84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10122,7 +10119,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10142,41 +10139,41 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E85" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K85" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="F85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K85" t="s" s="2">
+      <c r="L85" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10227,7 +10224,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10247,10 +10244,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10348,39 +10345,39 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E87" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K87" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="F87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10431,7 +10428,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -10451,10 +10448,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10479,11 +10476,11 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10534,7 +10531,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10554,10 +10551,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10655,10 +10652,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10687,7 +10684,7 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10699,7 +10696,7 @@
         <v>75</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>75</v>
@@ -10738,7 +10735,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -10758,17 +10755,17 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>81</v>
@@ -10790,7 +10787,7 @@
       </c>
       <c r="L91" s="2"/>
       <c r="M91" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10802,7 +10799,7 @@
         <v>75</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>75</v>
@@ -10841,7 +10838,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -10861,17 +10858,17 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>81</v>
@@ -10893,7 +10890,7 @@
       </c>
       <c r="L92" s="2"/>
       <c r="M92" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10905,7 +10902,7 @@
         <v>75</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>75</v>
@@ -10944,7 +10941,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -10964,17 +10961,17 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>81</v>
@@ -10996,7 +10993,7 @@
       </c>
       <c r="L93" s="2"/>
       <c r="M93" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11047,7 +11044,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -11067,17 +11064,17 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>81</v>
@@ -11099,7 +11096,7 @@
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11111,7 +11108,7 @@
         <v>75</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>75</v>
@@ -11150,7 +11147,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -11170,10 +11167,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11196,11 +11193,11 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11251,7 +11248,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -11271,10 +11268,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11301,7 +11298,7 @@
       </c>
       <c r="L96" s="2"/>
       <c r="M96" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11352,7 +11349,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -11372,39 +11369,39 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E97" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="F97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K97" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="F97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11455,7 +11452,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -11475,39 +11472,39 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E98" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="F98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K98" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="F98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11558,7 +11555,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -11578,17 +11575,17 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F99" t="s" s="2">
         <v>81</v>
@@ -11606,11 +11603,11 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11661,7 +11658,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -11681,10 +11678,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11709,13 +11706,13 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11766,7 +11763,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -11786,17 +11783,17 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>81</v>
@@ -11814,11 +11811,11 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11869,7 +11866,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -11889,10 +11886,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11906,7 +11903,7 @@
         <v>76</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>75</v>
@@ -11915,13 +11912,13 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11952,7 +11949,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>75</v>
@@ -11970,7 +11967,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -11990,10 +11987,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12016,7 +12013,7 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12045,11 +12042,11 @@
         <v>75</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>75</v>
@@ -12067,7 +12064,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12087,10 +12084,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12113,11 +12110,11 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12168,7 +12165,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12188,10 +12185,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12214,7 +12211,7 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12267,7 +12264,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -12287,10 +12284,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12313,7 +12310,7 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12366,7 +12363,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -12386,10 +12383,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12412,7 +12409,7 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12465,7 +12462,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -12485,10 +12482,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12511,13 +12508,13 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12568,7 +12565,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -12588,10 +12585,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12614,7 +12611,7 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12667,7 +12664,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -12687,10 +12684,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12713,7 +12710,7 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12766,7 +12763,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -12786,10 +12783,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12812,7 +12809,7 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12865,7 +12862,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -12885,10 +12882,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12911,7 +12908,7 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12964,7 +12961,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -12984,10 +12981,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13010,7 +13007,7 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13063,7 +13060,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13083,10 +13080,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13109,7 +13106,7 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13162,7 +13159,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13182,10 +13179,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13208,11 +13205,11 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13263,7 +13260,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13283,10 +13280,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13384,10 +13381,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13485,10 +13482,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13586,10 +13583,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13687,10 +13684,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13790,10 +13787,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13893,10 +13890,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13996,10 +13993,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14099,10 +14096,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14200,10 +14197,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14237,7 +14234,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>75</v>
@@ -14259,7 +14256,7 @@
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>75</v>
@@ -14277,7 +14274,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -14297,10 +14294,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14323,7 +14320,7 @@
         <v>75</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14376,7 +14373,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -14396,10 +14393,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14422,7 +14419,7 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14475,7 +14472,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-statut.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-statut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-statut.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-statut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-statut.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-statut.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
